--- a/example_files/RSV-B_metadata_template.xlsx
+++ b/example_files/RSV-B_metadata_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E05E0-D833-384B-8A55-BEF38F4A6B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4741BD-DA9B-EB45-AFF0-F358CFE8A06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18500" yWindow="-22100" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1555,7 +1555,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="873">
   <si>
     <t>id</t>
   </si>
@@ -4171,9 +4171,6 @@
   </si>
   <si>
     <t>Homo sapiens</t>
-  </si>
-  <si>
-    <t>29/03/2025</t>
   </si>
   <si>
     <t>MN-MDH-RSVB-02822</t>
@@ -4198,6 +4195,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4949,8 +4947,8 @@
       <c r="B2" t="s">
         <v>520</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>872</v>
+      <c r="C2" s="13">
+        <v>45745</v>
       </c>
       <c r="D2" t="s">
         <v>868</v>
@@ -4968,7 +4966,7 @@
         <v>870</v>
       </c>
       <c r="Q2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>
